--- a/Y英雄齿轮养成表.xlsx
+++ b/Y英雄齿轮养成表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="270">
   <si>
     <t>ID</t>
   </si>
@@ -837,11 +837,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -868,13 +868,6 @@
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -912,8 +905,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -935,6 +929,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -951,7 +969,51 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -959,30 +1021,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1005,52 +1043,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1113,13 +1106,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1131,7 +1118,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1143,13 +1142,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1161,19 +1208,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1185,91 +1226,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1287,13 +1244,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1378,6 +1371,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1389,6 +1397,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1417,50 +1445,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1475,151 +1459,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1646,79 +1639,79 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2067,7 +2060,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="20.25" customWidth="1"/>
@@ -2639,7 +2632,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" ht="18.6" customHeight="1" spans="1:8">
+    <row r="23" ht="21" customHeight="1" spans="1:8">
       <c r="A23" s="24">
         <v>120</v>
       </c>
@@ -2688,6 +2681,32 @@
         <v>71</v>
       </c>
       <c r="H24" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A25" s="24">
+        <v>120</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="32">
         <v>100</v>
       </c>
     </row>
